--- a/ACCTG320/datasets/05_etl_fields/Analytics_mindset_case_studies_ETL_Case2.xlsx
+++ b/ACCTG320/datasets/05_etl_fields/Analytics_mindset_case_studies_ETL_Case2.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\banksca\Documents\ARC\Curriculum\Analytics mindset\FINAL\ETL\Case 2-Text extraction and unique identifiers\Alteryx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github_connections\datasets.io\ACCTG320\datasets\05_etl_fields\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F8CCB2-D86E-452B-8175-85B533143B42}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61942AB-859C-4718-8AC3-19378987881D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20160" windowHeight="9576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5145" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Case 2" sheetId="3" r:id="rId1"/>
+    <sheet name="employees" sheetId="3" r:id="rId1"/>
+    <sheet name="plants" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="1515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="1654">
   <si>
     <t>Gerald</t>
   </si>
@@ -4570,6 +4582,423 @@
   </si>
   <si>
     <t>MEX1586-12W</t>
+  </si>
+  <si>
+    <t>country_plant_id</t>
+  </si>
+  <si>
+    <t>plant_type</t>
+  </si>
+  <si>
+    <t>ARG-15</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>GER-24</t>
+  </si>
+  <si>
+    <t>USA-12</t>
+  </si>
+  <si>
+    <t>AUS-21</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>CAN-20</t>
+  </si>
+  <si>
+    <t>Distribution</t>
+  </si>
+  <si>
+    <t>USA-20</t>
+  </si>
+  <si>
+    <t>ENG-22</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>GER-10</t>
+  </si>
+  <si>
+    <t>JAP-26</t>
+  </si>
+  <si>
+    <t>ARG-10</t>
+  </si>
+  <si>
+    <t>ARG-11</t>
+  </si>
+  <si>
+    <t>AUS-14</t>
+  </si>
+  <si>
+    <t>ENG-21</t>
+  </si>
+  <si>
+    <t>ENG-24</t>
+  </si>
+  <si>
+    <t>JAP-19</t>
+  </si>
+  <si>
+    <t>JAP-24</t>
+  </si>
+  <si>
+    <t>MEX-15</t>
+  </si>
+  <si>
+    <t>ARG-13</t>
+  </si>
+  <si>
+    <t>ARG-18</t>
+  </si>
+  <si>
+    <t>ARG-23</t>
+  </si>
+  <si>
+    <t>AUS-19</t>
+  </si>
+  <si>
+    <t>AUS-23</t>
+  </si>
+  <si>
+    <t>CAN-19</t>
+  </si>
+  <si>
+    <t>CAN-24</t>
+  </si>
+  <si>
+    <t>CAN-26</t>
+  </si>
+  <si>
+    <t>ENG-12</t>
+  </si>
+  <si>
+    <t>ENG-14</t>
+  </si>
+  <si>
+    <t>ENG-18</t>
+  </si>
+  <si>
+    <t>GER-12</t>
+  </si>
+  <si>
+    <t>JAP-13</t>
+  </si>
+  <si>
+    <t>JAP-16</t>
+  </si>
+  <si>
+    <t>JAP-18</t>
+  </si>
+  <si>
+    <t>JAP-21</t>
+  </si>
+  <si>
+    <t>MEX-12</t>
+  </si>
+  <si>
+    <t>MEX-14</t>
+  </si>
+  <si>
+    <t>MEX-17</t>
+  </si>
+  <si>
+    <t>USA-10</t>
+  </si>
+  <si>
+    <t>USA-14</t>
+  </si>
+  <si>
+    <t>USA-19</t>
+  </si>
+  <si>
+    <t>USA-21</t>
+  </si>
+  <si>
+    <t>USA-26</t>
+  </si>
+  <si>
+    <t>ARG-16</t>
+  </si>
+  <si>
+    <t>ARG-17</t>
+  </si>
+  <si>
+    <t>ARG-22</t>
+  </si>
+  <si>
+    <t>AUS-10</t>
+  </si>
+  <si>
+    <t>AUS-11</t>
+  </si>
+  <si>
+    <t>AUS-26</t>
+  </si>
+  <si>
+    <t>CAN-10</t>
+  </si>
+  <si>
+    <t>CAN-14</t>
+  </si>
+  <si>
+    <t>CAN-17</t>
+  </si>
+  <si>
+    <t>CAN-18</t>
+  </si>
+  <si>
+    <t>CAN-22</t>
+  </si>
+  <si>
+    <t>ENG-23</t>
+  </si>
+  <si>
+    <t>GER-11</t>
+  </si>
+  <si>
+    <t>GER-20</t>
+  </si>
+  <si>
+    <t>GER-21</t>
+  </si>
+  <si>
+    <t>JAP-11</t>
+  </si>
+  <si>
+    <t>JAP-15</t>
+  </si>
+  <si>
+    <t>JAP-23</t>
+  </si>
+  <si>
+    <t>JAP-25</t>
+  </si>
+  <si>
+    <t>MEX-11</t>
+  </si>
+  <si>
+    <t>MEX-23</t>
+  </si>
+  <si>
+    <t>MEX-26</t>
+  </si>
+  <si>
+    <t>USA-13</t>
+  </si>
+  <si>
+    <t>USA-23</t>
+  </si>
+  <si>
+    <t>ARG-12</t>
+  </si>
+  <si>
+    <t>ARG-14</t>
+  </si>
+  <si>
+    <t>ARG-19</t>
+  </si>
+  <si>
+    <t>ARG-25</t>
+  </si>
+  <si>
+    <t>AUS-13</t>
+  </si>
+  <si>
+    <t>AUS-16</t>
+  </si>
+  <si>
+    <t>AUS-17</t>
+  </si>
+  <si>
+    <t>AUS-18</t>
+  </si>
+  <si>
+    <t>AUS-24</t>
+  </si>
+  <si>
+    <t>CAN-12</t>
+  </si>
+  <si>
+    <t>CAN-16</t>
+  </si>
+  <si>
+    <t>ENG-20</t>
+  </si>
+  <si>
+    <t>ENG-26</t>
+  </si>
+  <si>
+    <t>GER-14</t>
+  </si>
+  <si>
+    <t>GER-16</t>
+  </si>
+  <si>
+    <t>GER-22</t>
+  </si>
+  <si>
+    <t>JAP-22</t>
+  </si>
+  <si>
+    <t>MEX-13</t>
+  </si>
+  <si>
+    <t>MEX-20</t>
+  </si>
+  <si>
+    <t>USA-15</t>
+  </si>
+  <si>
+    <t>USA-22</t>
+  </si>
+  <si>
+    <t>USA-25</t>
+  </si>
+  <si>
+    <t>ARG-20</t>
+  </si>
+  <si>
+    <t>ARG-21</t>
+  </si>
+  <si>
+    <t>ARG-26</t>
+  </si>
+  <si>
+    <t>AUS-22</t>
+  </si>
+  <si>
+    <t>CAN-13</t>
+  </si>
+  <si>
+    <t>CAN-23</t>
+  </si>
+  <si>
+    <t>ENG-11</t>
+  </si>
+  <si>
+    <t>ENG-13</t>
+  </si>
+  <si>
+    <t>ENG-15</t>
+  </si>
+  <si>
+    <t>GER-17</t>
+  </si>
+  <si>
+    <t>GER-25</t>
+  </si>
+  <si>
+    <t>JAP-10</t>
+  </si>
+  <si>
+    <t>JAP-17</t>
+  </si>
+  <si>
+    <t>MEX-10</t>
+  </si>
+  <si>
+    <t>MEX-22</t>
+  </si>
+  <si>
+    <t>MEX-24</t>
+  </si>
+  <si>
+    <t>MEX-25</t>
+  </si>
+  <si>
+    <t>USA-11</t>
+  </si>
+  <si>
+    <t>USA-16</t>
+  </si>
+  <si>
+    <t>USA-17</t>
+  </si>
+  <si>
+    <t>USA-18</t>
+  </si>
+  <si>
+    <t>USA-24</t>
+  </si>
+  <si>
+    <t>ARG-24</t>
+  </si>
+  <si>
+    <t>AUS-12</t>
+  </si>
+  <si>
+    <t>AUS-15</t>
+  </si>
+  <si>
+    <t>AUS-25</t>
+  </si>
+  <si>
+    <t>CAN-21</t>
+  </si>
+  <si>
+    <t>CAN-25</t>
+  </si>
+  <si>
+    <t>ENG-16</t>
+  </si>
+  <si>
+    <t>ENG-17</t>
+  </si>
+  <si>
+    <t>ENG-25</t>
+  </si>
+  <si>
+    <t>GER-18</t>
+  </si>
+  <si>
+    <t>GER-19</t>
+  </si>
+  <si>
+    <t>GER-26</t>
+  </si>
+  <si>
+    <t>JAP-12</t>
+  </si>
+  <si>
+    <t>JAP-20</t>
+  </si>
+  <si>
+    <t>MEX-16</t>
+  </si>
+  <si>
+    <t>MEX-19</t>
+  </si>
+  <si>
+    <t>MEX-21</t>
+  </si>
+  <si>
+    <t>AUS-20</t>
+  </si>
+  <si>
+    <t>CAN-11</t>
+  </si>
+  <si>
+    <t>GER-13</t>
+  </si>
+  <si>
+    <t>GER-15</t>
+  </si>
+  <si>
+    <t>GER-23</t>
+  </si>
+  <si>
+    <t>JAP-14</t>
+  </si>
+  <si>
+    <t>MEX-18</t>
   </si>
 </sst>
 </file>
@@ -4906,14 +5335,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C598"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>915</v>
       </c>
@@ -4924,7 +5353,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1374</v>
       </c>
@@ -4935,7 +5364,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1180</v>
       </c>
@@ -4946,7 +5375,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1187</v>
       </c>
@@ -4957,7 +5386,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1039</v>
       </c>
@@ -4968,7 +5397,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1020</v>
       </c>
@@ -4979,7 +5408,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>949</v>
       </c>
@@ -4990,7 +5419,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1267</v>
       </c>
@@ -5001,7 +5430,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1404</v>
       </c>
@@ -5012,7 +5441,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>964</v>
       </c>
@@ -5023,7 +5452,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1313</v>
       </c>
@@ -5034,7 +5463,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1206</v>
       </c>
@@ -5045,7 +5474,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>929</v>
       </c>
@@ -5056,7 +5485,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1096</v>
       </c>
@@ -5067,7 +5496,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1292</v>
       </c>
@@ -5078,7 +5507,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1124</v>
       </c>
@@ -5089,7 +5518,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1467</v>
       </c>
@@ -5100,7 +5529,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1302</v>
       </c>
@@ -5111,7 +5540,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1276</v>
       </c>
@@ -5122,7 +5551,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>924</v>
       </c>
@@ -5133,7 +5562,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1307</v>
       </c>
@@ -5144,7 +5573,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1491</v>
       </c>
@@ -5155,7 +5584,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1310</v>
       </c>
@@ -5166,7 +5595,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1171</v>
       </c>
@@ -5177,7 +5606,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1222</v>
       </c>
@@ -5188,7 +5617,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1160</v>
       </c>
@@ -5199,7 +5628,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1331</v>
       </c>
@@ -5210,7 +5639,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>977</v>
       </c>
@@ -5221,7 +5650,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1008</v>
       </c>
@@ -5232,7 +5661,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1393</v>
       </c>
@@ -5243,7 +5672,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>953</v>
       </c>
@@ -5254,7 +5683,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1238</v>
       </c>
@@ -5265,7 +5694,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>1312</v>
       </c>
@@ -5276,7 +5705,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>1507</v>
       </c>
@@ -5287,7 +5716,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>987</v>
       </c>
@@ -5298,7 +5727,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>1109</v>
       </c>
@@ -5309,7 +5738,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>954</v>
       </c>
@@ -5320,7 +5749,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1051</v>
       </c>
@@ -5331,7 +5760,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1221</v>
       </c>
@@ -5342,7 +5771,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1324</v>
       </c>
@@ -5353,7 +5782,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1359</v>
       </c>
@@ -5364,7 +5793,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1320</v>
       </c>
@@ -5375,7 +5804,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1473</v>
       </c>
@@ -5386,7 +5815,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1439</v>
       </c>
@@ -5397,7 +5826,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1309</v>
       </c>
@@ -5408,7 +5837,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1217</v>
       </c>
@@ -5419,7 +5848,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1246</v>
       </c>
@@ -5430,7 +5859,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1401</v>
       </c>
@@ -5441,7 +5870,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1265</v>
       </c>
@@ -5452,7 +5881,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1136</v>
       </c>
@@ -5463,7 +5892,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1423</v>
       </c>
@@ -5474,7 +5903,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1316</v>
       </c>
@@ -5485,7 +5914,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1371</v>
       </c>
@@ -5496,7 +5925,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1153</v>
       </c>
@@ -5507,7 +5936,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1235</v>
       </c>
@@ -5518,7 +5947,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>962</v>
       </c>
@@ -5529,7 +5958,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>933</v>
       </c>
@@ -5540,7 +5969,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1045</v>
       </c>
@@ -5551,7 +5980,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1501</v>
       </c>
@@ -5562,7 +5991,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1146</v>
       </c>
@@ -5573,7 +6002,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1259</v>
       </c>
@@ -5584,7 +6013,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>1117</v>
       </c>
@@ -5595,7 +6024,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>1225</v>
       </c>
@@ -5606,7 +6035,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1338</v>
       </c>
@@ -5617,7 +6046,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>1188</v>
       </c>
@@ -5628,7 +6057,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>1062</v>
       </c>
@@ -5639,7 +6068,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1030</v>
       </c>
@@ -5650,7 +6079,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1215</v>
       </c>
@@ -5661,7 +6090,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1212</v>
       </c>
@@ -5672,7 +6101,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1090</v>
       </c>
@@ -5683,7 +6112,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1298</v>
       </c>
@@ -5694,7 +6123,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>1279</v>
       </c>
@@ -5705,7 +6134,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>1137</v>
       </c>
@@ -5716,7 +6145,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>1154</v>
       </c>
@@ -5727,7 +6156,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>1058</v>
       </c>
@@ -5738,7 +6167,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>946</v>
       </c>
@@ -5749,7 +6178,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>1422</v>
       </c>
@@ -5760,7 +6189,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>1216</v>
       </c>
@@ -5771,7 +6200,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>1395</v>
       </c>
@@ -5782,7 +6211,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>1166</v>
       </c>
@@ -5793,7 +6222,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>1223</v>
       </c>
@@ -5804,7 +6233,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>1243</v>
       </c>
@@ -5815,7 +6244,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>999</v>
       </c>
@@ -5826,7 +6255,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>1397</v>
       </c>
@@ -5837,7 +6266,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>1048</v>
       </c>
@@ -5848,7 +6277,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1047</v>
       </c>
@@ -5859,7 +6288,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>1249</v>
       </c>
@@ -5870,7 +6299,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>1468</v>
       </c>
@@ -5881,7 +6310,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1069</v>
       </c>
@@ -5892,7 +6321,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>1151</v>
       </c>
@@ -5903,7 +6332,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>937</v>
       </c>
@@ -5914,7 +6343,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>1191</v>
       </c>
@@ -5925,7 +6354,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>1066</v>
       </c>
@@ -5936,7 +6365,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1506</v>
       </c>
@@ -5947,7 +6376,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>1266</v>
       </c>
@@ -5958,7 +6387,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>1197</v>
       </c>
@@ -5969,7 +6398,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>942</v>
       </c>
@@ -5980,7 +6409,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>1416</v>
       </c>
@@ -5991,7 +6420,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>1377</v>
       </c>
@@ -6002,7 +6431,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>1354</v>
       </c>
@@ -6013,7 +6442,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>1372</v>
       </c>
@@ -6024,7 +6453,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>1496</v>
       </c>
@@ -6035,7 +6464,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>989</v>
       </c>
@@ -6046,7 +6475,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>1455</v>
       </c>
@@ -6057,7 +6486,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>1425</v>
       </c>
@@ -6068,7 +6497,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>1111</v>
       </c>
@@ -6079,7 +6508,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>1156</v>
       </c>
@@ -6090,7 +6519,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>1408</v>
       </c>
@@ -6101,7 +6530,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>1184</v>
       </c>
@@ -6112,7 +6541,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>1268</v>
       </c>
@@ -6123,7 +6552,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>1380</v>
       </c>
@@ -6134,7 +6563,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1252</v>
       </c>
@@ -6145,7 +6574,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>1270</v>
       </c>
@@ -6156,7 +6585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>1214</v>
       </c>
@@ -6167,7 +6596,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>1413</v>
       </c>
@@ -6178,7 +6607,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>1470</v>
       </c>
@@ -6189,7 +6618,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1250</v>
       </c>
@@ -6200,7 +6629,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1283</v>
       </c>
@@ -6211,7 +6640,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1140</v>
       </c>
@@ -6222,7 +6651,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>1145</v>
       </c>
@@ -6233,7 +6662,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>944</v>
       </c>
@@ -6244,7 +6673,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>918</v>
       </c>
@@ -6255,7 +6684,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1092</v>
       </c>
@@ -6266,7 +6695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>1261</v>
       </c>
@@ -6277,7 +6706,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1245</v>
       </c>
@@ -6288,7 +6717,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>1094</v>
       </c>
@@ -6299,7 +6728,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>1049</v>
       </c>
@@ -6310,7 +6739,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>1132</v>
       </c>
@@ -6321,7 +6750,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>1264</v>
       </c>
@@ -6332,7 +6761,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1247</v>
       </c>
@@ -6343,7 +6772,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>1241</v>
       </c>
@@ -6354,7 +6783,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>1244</v>
       </c>
@@ -6365,7 +6794,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1285</v>
       </c>
@@ -6376,7 +6805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>943</v>
       </c>
@@ -6387,7 +6816,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>1125</v>
       </c>
@@ -6398,7 +6827,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1251</v>
       </c>
@@ -6409,7 +6838,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>1163</v>
       </c>
@@ -6420,7 +6849,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>1392</v>
       </c>
@@ -6431,7 +6860,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1297</v>
       </c>
@@ -6442,7 +6871,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>1332</v>
       </c>
@@ -6453,7 +6882,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>1459</v>
       </c>
@@ -6464,7 +6893,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>1378</v>
       </c>
@@ -6475,7 +6904,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>1193</v>
       </c>
@@ -6486,7 +6915,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>1409</v>
       </c>
@@ -6497,7 +6926,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>1202</v>
       </c>
@@ -6508,7 +6937,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>1159</v>
       </c>
@@ -6519,7 +6948,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>1514</v>
       </c>
@@ -6530,7 +6959,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>1112</v>
       </c>
@@ -6541,7 +6970,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>1434</v>
       </c>
@@ -6552,7 +6981,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1059</v>
       </c>
@@ -6563,7 +6992,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>1054</v>
       </c>
@@ -6574,7 +7003,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>1495</v>
       </c>
@@ -6585,7 +7014,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>1344</v>
       </c>
@@ -6596,7 +7025,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>1201</v>
       </c>
@@ -6607,7 +7036,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>1120</v>
       </c>
@@ -6618,7 +7047,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>1053</v>
       </c>
@@ -6629,7 +7058,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>1148</v>
       </c>
@@ -6640,7 +7069,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>1123</v>
       </c>
@@ -6651,7 +7080,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>1104</v>
       </c>
@@ -6662,7 +7091,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>1106</v>
       </c>
@@ -6673,7 +7102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>940</v>
       </c>
@@ -6684,7 +7113,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1056</v>
       </c>
@@ -6695,7 +7124,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1083</v>
       </c>
@@ -6706,7 +7135,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1511</v>
       </c>
@@ -6717,7 +7146,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1346</v>
       </c>
@@ -6728,7 +7157,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>1006</v>
       </c>
@@ -6739,7 +7168,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>1355</v>
       </c>
@@ -6750,7 +7179,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1022</v>
       </c>
@@ -6761,7 +7190,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>1074</v>
       </c>
@@ -6772,7 +7201,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>957</v>
       </c>
@@ -6783,7 +7212,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>1234</v>
       </c>
@@ -6794,7 +7223,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>1358</v>
       </c>
@@ -6805,7 +7234,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1004</v>
       </c>
@@ -6816,7 +7245,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>1379</v>
       </c>
@@ -6827,7 +7256,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>1107</v>
       </c>
@@ -6838,7 +7267,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>938</v>
       </c>
@@ -6849,7 +7278,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>1179</v>
       </c>
@@ -6860,7 +7289,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>1255</v>
       </c>
@@ -6871,7 +7300,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>1018</v>
       </c>
@@ -6882,7 +7311,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>1463</v>
       </c>
@@ -6893,7 +7322,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>1063</v>
       </c>
@@ -6904,7 +7333,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>1477</v>
       </c>
@@ -6915,7 +7344,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>1509</v>
       </c>
@@ -6926,7 +7355,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>994</v>
       </c>
@@ -6937,7 +7366,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>1144</v>
       </c>
@@ -6948,7 +7377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>1391</v>
       </c>
@@ -6959,7 +7388,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>1290</v>
       </c>
@@ -6970,7 +7399,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1113</v>
       </c>
@@ -6981,7 +7410,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>1043</v>
       </c>
@@ -6992,7 +7421,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>1023</v>
       </c>
@@ -7003,7 +7432,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1339</v>
       </c>
@@ -7014,7 +7443,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>1178</v>
       </c>
@@ -7025,7 +7454,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>948</v>
       </c>
@@ -7036,7 +7465,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>1147</v>
       </c>
@@ -7047,7 +7476,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1014</v>
       </c>
@@ -7058,7 +7487,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>1028</v>
       </c>
@@ -7069,7 +7498,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1126</v>
       </c>
@@ -7080,7 +7509,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>1494</v>
       </c>
@@ -7091,7 +7520,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>1034</v>
       </c>
@@ -7102,7 +7531,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1260</v>
       </c>
@@ -7113,7 +7542,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>1438</v>
       </c>
@@ -7124,7 +7553,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>996</v>
       </c>
@@ -7135,7 +7564,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>1091</v>
       </c>
@@ -7146,7 +7575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>1428</v>
       </c>
@@ -7157,7 +7586,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>927</v>
       </c>
@@ -7168,7 +7597,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>1046</v>
       </c>
@@ -7179,7 +7608,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1492</v>
       </c>
@@ -7190,7 +7619,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1177</v>
       </c>
@@ -7201,7 +7630,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1263</v>
       </c>
@@ -7212,7 +7641,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1205</v>
       </c>
@@ -7223,7 +7652,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1032</v>
       </c>
@@ -7234,7 +7663,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>1336</v>
       </c>
@@ -7245,7 +7674,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1055</v>
       </c>
@@ -7256,7 +7685,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>1129</v>
       </c>
@@ -7267,7 +7696,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>1275</v>
       </c>
@@ -7278,7 +7707,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>947</v>
       </c>
@@ -7289,7 +7718,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>1007</v>
       </c>
@@ -7300,7 +7729,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>1052</v>
       </c>
@@ -7311,7 +7740,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1351</v>
       </c>
@@ -7322,7 +7751,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1042</v>
       </c>
@@ -7333,7 +7762,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>1027</v>
       </c>
@@ -7344,7 +7773,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1071</v>
       </c>
@@ -7355,7 +7784,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1230</v>
       </c>
@@ -7366,7 +7795,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>1152</v>
       </c>
@@ -7377,7 +7806,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1239</v>
       </c>
@@ -7388,7 +7817,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>978</v>
       </c>
@@ -7399,7 +7828,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>1073</v>
       </c>
@@ -7410,7 +7839,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1387</v>
       </c>
@@ -7421,7 +7850,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>1116</v>
       </c>
@@ -7432,7 +7861,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>1060</v>
       </c>
@@ -7443,7 +7872,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>1278</v>
       </c>
@@ -7454,7 +7883,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1490</v>
       </c>
@@ -7465,7 +7894,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>1412</v>
       </c>
@@ -7476,7 +7905,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>1445</v>
       </c>
@@ -7487,7 +7916,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>1437</v>
       </c>
@@ -7498,7 +7927,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1075</v>
       </c>
@@ -7509,7 +7938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1421</v>
       </c>
@@ -7520,7 +7949,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>1143</v>
       </c>
@@ -7531,7 +7960,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>1474</v>
       </c>
@@ -7542,7 +7971,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>1364</v>
       </c>
@@ -7553,7 +7982,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>1190</v>
       </c>
@@ -7564,7 +7993,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>1450</v>
       </c>
@@ -7575,7 +8004,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1038</v>
       </c>
@@ -7586,7 +8015,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1157</v>
       </c>
@@ -7597,7 +8026,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1100</v>
       </c>
@@ -7608,7 +8037,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1453</v>
       </c>
@@ -7619,7 +8048,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1119</v>
       </c>
@@ -7630,7 +8059,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1503</v>
       </c>
@@ -7641,7 +8070,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>1308</v>
       </c>
@@ -7652,7 +8081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>1176</v>
       </c>
@@ -7663,7 +8092,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>1122</v>
       </c>
@@ -7674,7 +8103,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1169</v>
       </c>
@@ -7685,7 +8114,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1232</v>
       </c>
@@ -7696,7 +8125,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1015</v>
       </c>
@@ -7707,7 +8136,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>969</v>
       </c>
@@ -7718,7 +8147,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1199</v>
       </c>
@@ -7729,7 +8158,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1057</v>
       </c>
@@ -7740,7 +8169,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1210</v>
       </c>
@@ -7751,7 +8180,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>1195</v>
       </c>
@@ -7762,7 +8191,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1362</v>
       </c>
@@ -7773,7 +8202,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1218</v>
       </c>
@@ -7784,7 +8213,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1061</v>
       </c>
@@ -7795,7 +8224,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1149</v>
       </c>
@@ -7806,7 +8235,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1105</v>
       </c>
@@ -7817,7 +8246,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1341</v>
       </c>
@@ -7828,7 +8257,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1370</v>
       </c>
@@ -7839,7 +8268,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1375</v>
       </c>
@@ -7850,7 +8279,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1208</v>
       </c>
@@ -7861,7 +8290,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>982</v>
       </c>
@@ -7872,7 +8301,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>922</v>
       </c>
@@ -7883,7 +8312,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1465</v>
       </c>
@@ -7894,7 +8323,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1315</v>
       </c>
@@ -7905,7 +8334,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1497</v>
       </c>
@@ -7916,7 +8345,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1084</v>
       </c>
@@ -7927,7 +8356,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1480</v>
       </c>
@@ -7938,7 +8367,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1405</v>
       </c>
@@ -7949,7 +8378,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>926</v>
       </c>
@@ -7960,7 +8389,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1080</v>
       </c>
@@ -7971,7 +8400,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1376</v>
       </c>
@@ -7982,7 +8411,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1040</v>
       </c>
@@ -7993,7 +8422,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1347</v>
       </c>
@@ -8004,7 +8433,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>945</v>
       </c>
@@ -8015,7 +8444,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1328</v>
       </c>
@@ -8026,7 +8455,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1016</v>
       </c>
@@ -8037,7 +8466,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1133</v>
       </c>
@@ -8048,7 +8477,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1131</v>
       </c>
@@ -8059,7 +8488,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1488</v>
       </c>
@@ -8070,7 +8499,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1418</v>
       </c>
@@ -8081,7 +8510,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1170</v>
       </c>
@@ -8092,7 +8521,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1025</v>
       </c>
@@ -8103,7 +8532,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1323</v>
       </c>
@@ -8114,7 +8543,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1085</v>
       </c>
@@ -8125,7 +8554,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1357</v>
       </c>
@@ -8136,7 +8565,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1303</v>
       </c>
@@ -8147,7 +8576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>986</v>
       </c>
@@ -8158,7 +8587,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1340</v>
       </c>
@@ -8169,7 +8598,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1226</v>
       </c>
@@ -8180,7 +8609,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>976</v>
       </c>
@@ -8191,7 +8620,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1229</v>
       </c>
@@ -8202,7 +8631,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1482</v>
       </c>
@@ -8213,7 +8642,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>959</v>
       </c>
@@ -8224,7 +8653,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1481</v>
       </c>
@@ -8235,7 +8664,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>932</v>
       </c>
@@ -8246,7 +8675,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>973</v>
       </c>
@@ -8257,7 +8686,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1050</v>
       </c>
@@ -8268,7 +8697,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1489</v>
       </c>
@@ -8279,7 +8708,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1317</v>
       </c>
@@ -8290,7 +8719,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1469</v>
       </c>
@@ -8301,7 +8730,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>928</v>
       </c>
@@ -8312,7 +8741,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1442</v>
       </c>
@@ -8323,7 +8752,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1410</v>
       </c>
@@ -8334,7 +8763,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>920</v>
       </c>
@@ -8345,7 +8774,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1127</v>
       </c>
@@ -8356,7 +8785,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1162</v>
       </c>
@@ -8367,7 +8796,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1135</v>
       </c>
@@ -8378,7 +8807,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>1411</v>
       </c>
@@ -8389,7 +8818,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1000</v>
       </c>
@@ -8400,7 +8829,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1141</v>
       </c>
@@ -8411,7 +8840,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1508</v>
       </c>
@@ -8422,7 +8851,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1089</v>
       </c>
@@ -8433,7 +8862,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1231</v>
       </c>
@@ -8444,7 +8873,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1087</v>
       </c>
@@ -8455,7 +8884,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1076</v>
       </c>
@@ -8466,7 +8895,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1065</v>
       </c>
@@ -8477,7 +8906,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1093</v>
       </c>
@@ -8488,7 +8917,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>958</v>
       </c>
@@ -8499,7 +8928,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1254</v>
       </c>
@@ -8510,7 +8939,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1318</v>
       </c>
@@ -8521,7 +8950,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>936</v>
       </c>
@@ -8532,7 +8961,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1360</v>
       </c>
@@ -8543,7 +8972,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>1103</v>
       </c>
@@ -8554,7 +8983,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1031</v>
       </c>
@@ -8565,7 +8994,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1036</v>
       </c>
@@ -8576,7 +9005,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1419</v>
       </c>
@@ -8587,7 +9016,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1064</v>
       </c>
@@ -8598,7 +9027,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1282</v>
       </c>
@@ -8609,7 +9038,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>921</v>
       </c>
@@ -8620,7 +9049,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1436</v>
       </c>
@@ -8631,7 +9060,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1262</v>
       </c>
@@ -8642,7 +9071,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1300</v>
       </c>
@@ -8653,7 +9082,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1118</v>
       </c>
@@ -8664,7 +9093,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1400</v>
       </c>
@@ -8675,7 +9104,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1352</v>
       </c>
@@ -8686,7 +9115,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>979</v>
       </c>
@@ -8697,7 +9126,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>983</v>
       </c>
@@ -8708,7 +9137,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1168</v>
       </c>
@@ -8719,7 +9148,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1068</v>
       </c>
@@ -8730,7 +9159,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1386</v>
       </c>
@@ -8741,7 +9170,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1390</v>
       </c>
@@ -8752,7 +9181,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1203</v>
       </c>
@@ -8763,7 +9192,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1389</v>
       </c>
@@ -8774,7 +9203,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1460</v>
       </c>
@@ -8785,7 +9214,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1327</v>
       </c>
@@ -8796,7 +9225,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1021</v>
       </c>
@@ -8807,7 +9236,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1510</v>
       </c>
@@ -8818,7 +9247,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1121</v>
       </c>
@@ -8829,7 +9258,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1451</v>
       </c>
@@ -8840,7 +9269,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1209</v>
       </c>
@@ -8851,7 +9280,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1274</v>
       </c>
@@ -8862,7 +9291,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>975</v>
       </c>
@@ -8873,7 +9302,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1301</v>
       </c>
@@ -8884,7 +9313,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1305</v>
       </c>
@@ -8895,7 +9324,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1314</v>
       </c>
@@ -8906,7 +9335,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1172</v>
       </c>
@@ -8917,7 +9346,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1343</v>
       </c>
@@ -8928,7 +9357,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1399</v>
       </c>
@@ -8939,7 +9368,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1253</v>
       </c>
@@ -8950,7 +9379,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1367</v>
       </c>
@@ -8961,7 +9390,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>960</v>
       </c>
@@ -8972,7 +9401,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1430</v>
       </c>
@@ -8983,7 +9412,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>919</v>
       </c>
@@ -8994,7 +9423,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>998</v>
       </c>
@@ -9005,7 +9434,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1198</v>
       </c>
@@ -9016,7 +9445,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1472</v>
       </c>
@@ -9027,7 +9456,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1415</v>
       </c>
@@ -9038,7 +9467,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>935</v>
       </c>
@@ -9049,7 +9478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1293</v>
       </c>
@@ -9060,7 +9489,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>923</v>
       </c>
@@ -9071,7 +9500,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1329</v>
       </c>
@@ -9082,7 +9511,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1019</v>
       </c>
@@ -9093,7 +9522,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>952</v>
       </c>
@@ -9104,7 +9533,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>990</v>
       </c>
@@ -9115,7 +9544,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>963</v>
       </c>
@@ -9126,7 +9555,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1227</v>
       </c>
@@ -9137,7 +9566,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1504</v>
       </c>
@@ -9148,7 +9577,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1424</v>
       </c>
@@ -9159,7 +9588,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1139</v>
       </c>
@@ -9170,7 +9599,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1306</v>
       </c>
@@ -9181,7 +9610,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1142</v>
       </c>
@@ -9192,7 +9621,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1211</v>
       </c>
@@ -9203,7 +9632,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1350</v>
       </c>
@@ -9214,7 +9643,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1443</v>
       </c>
@@ -9225,7 +9654,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1348</v>
       </c>
@@ -9236,7 +9665,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1150</v>
       </c>
@@ -9247,7 +9676,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1186</v>
       </c>
@@ -9258,7 +9687,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>970</v>
       </c>
@@ -9269,7 +9698,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1456</v>
       </c>
@@ -9280,7 +9709,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1487</v>
       </c>
@@ -9291,7 +9720,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1366</v>
       </c>
@@ -9302,7 +9731,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1342</v>
       </c>
@@ -9313,7 +9742,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1256</v>
       </c>
@@ -9324,7 +9753,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>965</v>
       </c>
@@ -9335,7 +9764,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1284</v>
       </c>
@@ -9346,7 +9775,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1114</v>
       </c>
@@ -9357,7 +9786,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1446</v>
       </c>
@@ -9368,7 +9797,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>939</v>
       </c>
@@ -9379,7 +9808,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1295</v>
       </c>
@@ -9390,7 +9819,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1240</v>
       </c>
@@ -9401,7 +9830,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1078</v>
       </c>
@@ -9412,7 +9841,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>931</v>
       </c>
@@ -9423,7 +9852,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1182</v>
       </c>
@@ -9434,7 +9863,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1383</v>
       </c>
@@ -9445,7 +9874,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1200</v>
       </c>
@@ -9456,7 +9885,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1289</v>
       </c>
@@ -9467,7 +9896,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1385</v>
       </c>
@@ -9478,7 +9907,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1384</v>
       </c>
@@ -9489,7 +9918,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1448</v>
       </c>
@@ -9500,7 +9929,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>981</v>
       </c>
@@ -9511,7 +9940,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1403</v>
       </c>
@@ -9522,7 +9951,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1505</v>
       </c>
@@ -9533,7 +9962,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1161</v>
       </c>
@@ -9544,7 +9973,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1175</v>
       </c>
@@ -9555,7 +9984,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1325</v>
       </c>
@@ -9566,7 +9995,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1228</v>
       </c>
@@ -9577,7 +10006,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1464</v>
       </c>
@@ -9588,7 +10017,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1478</v>
       </c>
@@ -9599,7 +10028,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1070</v>
       </c>
@@ -9610,7 +10039,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1099</v>
       </c>
@@ -9621,7 +10050,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1072</v>
       </c>
@@ -9632,7 +10061,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1502</v>
       </c>
@@ -9643,7 +10072,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1013</v>
       </c>
@@ -9654,7 +10083,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1128</v>
       </c>
@@ -9665,7 +10094,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1233</v>
       </c>
@@ -9676,7 +10105,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1500</v>
       </c>
@@ -9687,7 +10116,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1513</v>
       </c>
@@ -9698,7 +10127,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1181</v>
       </c>
@@ -9709,7 +10138,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1287</v>
       </c>
@@ -9720,7 +10149,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1435</v>
       </c>
@@ -9731,7 +10160,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>934</v>
       </c>
@@ -9742,7 +10171,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>966</v>
       </c>
@@ -9753,7 +10182,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>968</v>
       </c>
@@ -9764,7 +10193,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1432</v>
       </c>
@@ -9775,7 +10204,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1044</v>
       </c>
@@ -9786,7 +10215,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>967</v>
       </c>
@@ -9797,7 +10226,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1334</v>
       </c>
@@ -9808,7 +10237,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1311</v>
       </c>
@@ -9819,7 +10248,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1484</v>
       </c>
@@ -9830,7 +10259,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1189</v>
       </c>
@@ -9841,7 +10270,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1512</v>
       </c>
@@ -9852,7 +10281,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1486</v>
       </c>
@@ -9863,7 +10292,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1431</v>
       </c>
@@ -9874,7 +10303,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>1281</v>
       </c>
@@ -9885,7 +10314,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1294</v>
       </c>
@@ -9896,7 +10325,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>1185</v>
       </c>
@@ -9907,7 +10336,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>1009</v>
       </c>
@@ -9918,7 +10347,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>1499</v>
       </c>
@@ -9929,7 +10358,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>1286</v>
       </c>
@@ -9940,7 +10369,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1394</v>
       </c>
@@ -9951,7 +10380,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1095</v>
       </c>
@@ -9962,7 +10391,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1291</v>
       </c>
@@ -9973,7 +10402,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>941</v>
       </c>
@@ -9984,7 +10413,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1220</v>
       </c>
@@ -9995,7 +10424,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>1433</v>
       </c>
@@ -10006,7 +10435,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>971</v>
       </c>
@@ -10017,7 +10446,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1033</v>
       </c>
@@ -10028,7 +10457,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1498</v>
       </c>
@@ -10039,7 +10468,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1167</v>
       </c>
@@ -10050,7 +10479,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1110</v>
       </c>
@@ -10061,7 +10490,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1155</v>
       </c>
@@ -10072,7 +10501,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1322</v>
       </c>
@@ -10083,7 +10512,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1010</v>
       </c>
@@ -10094,7 +10523,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1466</v>
       </c>
@@ -10105,7 +10534,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1441</v>
       </c>
@@ -10116,7 +10545,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>985</v>
       </c>
@@ -10127,7 +10556,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1102</v>
       </c>
@@ -10138,7 +10567,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1269</v>
       </c>
@@ -10149,7 +10578,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1003</v>
       </c>
@@ -10160,7 +10589,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>956</v>
       </c>
@@ -10171,7 +10600,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1476</v>
       </c>
@@ -10182,7 +10611,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1041</v>
       </c>
@@ -10193,7 +10622,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>1207</v>
       </c>
@@ -10204,7 +10633,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1098</v>
       </c>
@@ -10215,7 +10644,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>1363</v>
       </c>
@@ -10226,7 +10655,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1321</v>
       </c>
@@ -10237,7 +10666,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>1077</v>
       </c>
@@ -10248,7 +10677,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>1319</v>
       </c>
@@ -10259,7 +10688,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>991</v>
       </c>
@@ -10270,7 +10699,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>1115</v>
       </c>
@@ -10281,7 +10710,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>1449</v>
       </c>
@@ -10292,7 +10721,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1097</v>
       </c>
@@ -10303,7 +10732,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>1417</v>
       </c>
@@ -10314,7 +10743,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>980</v>
       </c>
@@ -10325,7 +10754,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>1333</v>
       </c>
@@ -10336,7 +10765,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>1356</v>
       </c>
@@ -10347,7 +10776,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1398</v>
       </c>
@@ -10358,7 +10787,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>1458</v>
       </c>
@@ -10369,7 +10798,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>1248</v>
       </c>
@@ -10380,7 +10809,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>1414</v>
       </c>
@@ -10391,7 +10820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1299</v>
       </c>
@@ -10402,7 +10831,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>1219</v>
       </c>
@@ -10413,7 +10842,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>1296</v>
       </c>
@@ -10424,7 +10853,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>1381</v>
       </c>
@@ -10435,7 +10864,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>1035</v>
       </c>
@@ -10446,7 +10875,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>951</v>
       </c>
@@ -10457,7 +10886,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>1224</v>
       </c>
@@ -10468,7 +10897,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>1396</v>
       </c>
@@ -10479,7 +10908,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>984</v>
       </c>
@@ -10490,7 +10919,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>995</v>
       </c>
@@ -10501,7 +10930,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>1173</v>
       </c>
@@ -10512,7 +10941,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>1242</v>
       </c>
@@ -10523,7 +10952,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>1402</v>
       </c>
@@ -10534,7 +10963,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>1420</v>
       </c>
@@ -10545,7 +10974,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>1272</v>
       </c>
@@ -10556,7 +10985,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>1485</v>
       </c>
@@ -10567,7 +10996,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>972</v>
       </c>
@@ -10578,7 +11007,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>930</v>
       </c>
@@ -10589,7 +11018,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>1330</v>
       </c>
@@ -10600,7 +11029,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>1426</v>
       </c>
@@ -10611,7 +11040,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>988</v>
       </c>
@@ -10622,7 +11051,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>1088</v>
       </c>
@@ -10633,7 +11062,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>1454</v>
       </c>
@@ -10644,7 +11073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>1196</v>
       </c>
@@ -10655,7 +11084,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>1001</v>
       </c>
@@ -10666,7 +11095,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>1192</v>
       </c>
@@ -10677,7 +11106,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>1353</v>
       </c>
@@ -10688,7 +11117,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>1029</v>
       </c>
@@ -10699,7 +11128,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>1204</v>
       </c>
@@ -10710,7 +11139,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>1479</v>
       </c>
@@ -10721,7 +11150,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>1067</v>
       </c>
@@ -10732,7 +11161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>1236</v>
       </c>
@@ -10743,7 +11172,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>993</v>
       </c>
@@ -10754,7 +11183,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>1086</v>
       </c>
@@ -10765,7 +11194,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>1483</v>
       </c>
@@ -10776,7 +11205,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>1174</v>
       </c>
@@ -10787,7 +11216,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>1079</v>
       </c>
@@ -10798,7 +11227,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>1183</v>
       </c>
@@ -10809,7 +11238,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>950</v>
       </c>
@@ -10820,7 +11249,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>1164</v>
       </c>
@@ -10831,7 +11260,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>1134</v>
       </c>
@@ -10842,7 +11271,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>1345</v>
       </c>
@@ -10853,7 +11282,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>1471</v>
       </c>
@@ -10864,7 +11293,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>1002</v>
       </c>
@@ -10875,7 +11304,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>1158</v>
       </c>
@@ -10886,7 +11315,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>1082</v>
       </c>
@@ -10897,7 +11326,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>1493</v>
       </c>
@@ -10908,7 +11337,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>1130</v>
       </c>
@@ -10919,7 +11348,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>1277</v>
       </c>
@@ -10930,7 +11359,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>1273</v>
       </c>
@@ -10941,7 +11370,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>1011</v>
       </c>
@@ -10952,7 +11381,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>974</v>
       </c>
@@ -10963,7 +11392,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>955</v>
       </c>
@@ -10974,7 +11403,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>1373</v>
       </c>
@@ -10985,7 +11414,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>1326</v>
       </c>
@@ -10996,7 +11425,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>1271</v>
       </c>
@@ -11007,7 +11436,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>997</v>
       </c>
@@ -11018,7 +11447,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>1361</v>
       </c>
@@ -11029,7 +11458,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>1288</v>
       </c>
@@ -11040,7 +11469,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>1369</v>
       </c>
@@ -11051,7 +11480,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>961</v>
       </c>
@@ -11062,7 +11491,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>1026</v>
       </c>
@@ -11073,7 +11502,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>1407</v>
       </c>
@@ -11084,7 +11513,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>992</v>
       </c>
@@ -11095,7 +11524,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>1337</v>
       </c>
@@ -11106,7 +11535,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>925</v>
       </c>
@@ -11117,7 +11546,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>1194</v>
       </c>
@@ -11128,7 +11557,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>1024</v>
       </c>
@@ -11139,7 +11568,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>1108</v>
       </c>
@@ -11150,7 +11579,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>1165</v>
       </c>
@@ -11161,7 +11590,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>1349</v>
       </c>
@@ -11172,7 +11601,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>1440</v>
       </c>
@@ -11183,7 +11612,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>1368</v>
       </c>
@@ -11194,7 +11623,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>1280</v>
       </c>
@@ -11205,7 +11634,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>1213</v>
       </c>
@@ -11216,7 +11645,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>1444</v>
       </c>
@@ -11227,7 +11656,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>1081</v>
       </c>
@@ -11238,7 +11667,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>1101</v>
       </c>
@@ -11249,7 +11678,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>1005</v>
       </c>
@@ -11260,7 +11689,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>1012</v>
       </c>
@@ -11271,7 +11700,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>1017</v>
       </c>
@@ -11282,7 +11711,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>1237</v>
       </c>
@@ -11293,7 +11722,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>1452</v>
       </c>
@@ -11304,7 +11733,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>1304</v>
       </c>
@@ -11315,7 +11744,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>1461</v>
       </c>
@@ -11326,7 +11755,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>1406</v>
       </c>
@@ -11337,7 +11766,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>1462</v>
       </c>
@@ -11348,7 +11777,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>1429</v>
       </c>
@@ -11359,7 +11788,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>1335</v>
       </c>
@@ -11370,7 +11799,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>1382</v>
       </c>
@@ -11381,7 +11810,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>1457</v>
       </c>
@@ -11392,7 +11821,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>1475</v>
       </c>
@@ -11403,7 +11832,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>1365</v>
       </c>
@@ -11414,7 +11843,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>1258</v>
       </c>
@@ -11425,7 +11854,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>1388</v>
       </c>
@@ -11436,7 +11865,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>1037</v>
       </c>
@@ -11447,7 +11876,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>1257</v>
       </c>
@@ -11458,7 +11887,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>1138</v>
       </c>
@@ -11469,7 +11898,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>1447</v>
       </c>
@@ -11480,7 +11909,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>1427</v>
       </c>
@@ -11489,6 +11918,1088 @@
       </c>
       <c r="C598" t="s">
         <v>470</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE44F89-A938-4E2E-8B3D-5BC4C3FC0821}">
+  <dimension ref="A1:B134"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1518</v>
       </c>
     </row>
   </sheetData>

--- a/ACCTG320/datasets/05_etl_fields/Analytics_mindset_case_studies_ETL_Case2.xlsx
+++ b/ACCTG320/datasets/05_etl_fields/Analytics_mindset_case_studies_ETL_Case2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A61942AB-859C-4718-8AC3-19378987881D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5145" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5145" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="employees" sheetId="3" r:id="rId1"/>
